--- a/Development/Master Log Starting 251003.xlsx
+++ b/Development/Master Log Starting 251003.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Stethoscope_Project\Development\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{606BAD65-BF25-405F-A0EB-0E5EBC6081A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35CF1891-41AB-465F-BF2A-59D009C70E70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-11085" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
-    <sheet name="Ensemble Model" sheetId="4" r:id="rId2"/>
-    <sheet name="Segmentation &amp; Label" sheetId="2" r:id="rId3"/>
-    <sheet name="Pre-Processing" sheetId="3" r:id="rId4"/>
+    <sheet name="Data Augmentation" sheetId="5" r:id="rId2"/>
+    <sheet name="Ensemble Model" sheetId="4" r:id="rId3"/>
+    <sheet name="Segmentation &amp; Label" sheetId="2" r:id="rId4"/>
+    <sheet name="Pre-Processing" sheetId="3" r:id="rId5"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="172">
   <si>
     <t>Date</t>
   </si>
@@ -73,15 +74,6 @@
   </si>
   <si>
     <t>Pre-Processing</t>
-  </si>
-  <si>
-    <t>Preprocessing 1</t>
-  </si>
-  <si>
-    <t>Pre Processing 2</t>
-  </si>
-  <si>
-    <t>Pre Processing 3</t>
   </si>
   <si>
     <t>PP-1</t>
@@ -659,6 +651,195 @@
   </si>
   <si>
     <t>Balanced Softmax(분포 보정)로 소수 클래스 상향, NB guard 사다리 유지</t>
+  </si>
+  <si>
+    <t>D:\Stethoscope_Project\Development\OPERA_Copied_from_Ubuntu\scripts\GPT\step16A_cosine_head_then_tau.py</t>
+  </si>
+  <si>
+    <t>Cosine(s=16) + CE + WeightedRandomSampler + per-class τ search (NB precision≥0.35), epochs=60, lr=3e-4, wd=1e-4</t>
+  </si>
+  <si>
+    <t>raw→τ: 0.291→0.392 (+0.101); tag=Step16A_CosHead_tau_NBprec_ge_0.35; 결과 디렉토리=...scripts\GPT\results_step16A\Step16A_CosHead_tau_NBprec_ge_0.35_* ; 폴드별 train_log.csv / confusion_matrix_tau.csv / taus.npy 저장</t>
+  </si>
+  <si>
+    <t>D:\Stethoscope_Project\Development\OPERA_Copied_from_Ubuntu\scripts\GPT\step16C_ensemble_cos_ldam_then_tau.py</t>
+  </si>
+  <si>
+    <t>Ensemble [Cosine(s=32)×3 + LDAM-DRW×3] prob-avg + per-class τ (NB precision≥0.35), epochs=60, lr=3e-4, wd=1e-4</t>
+  </si>
+  <si>
+    <t>per-fold tauMR=[0.411, 0.527, 0.318, 0.451, 0.307]; NB-prec≈[0.840, 0.955, 0.699, 0.818, 0.702]; 결과: ...\results_step16C\Step16C_Ensemble_Cos_s32__LDAM_DRW_seeds3_tau_NBprec_ge_0.35_*</t>
+  </si>
+  <si>
+    <t>D:\Stethoscope_Project\Development\OPERA_Copied_from_Ubuntu\scripts\GPT\step16D_cost_sensitive_tau.py</t>
+  </si>
+  <si>
+    <t>Linear + LDAM(DRW half) + cost-sensitive τ (w_c, recall floors, NB-prec≥0.35), epochs=60, lr=3e-4, wd=1e-4</t>
+  </si>
+  <si>
+    <t>per-fold tauMR=&lt;[...]&gt;; NB-prec=&lt;[...]&gt;; floors/weights/λ 기록</t>
+  </si>
+  <si>
+    <t>D:\Stethoscope_Project\Development\OPERA_Copied_from_Ubuntu\scripts\GPT\step16B_ldam_drw_then_tau.py</t>
+  </si>
+  <si>
+    <t>Linear + LDAM (second half DRW), epochs=60, lr=3e-4, wd=1e-4 + per-class τ (NB precision≥0.35)</t>
+  </si>
+  <si>
+    <t>per-fold tauMR=[0.418, 0.526, 0.427, 0.447, 0.310]; NB-prec=[0.875, 0.953, 0.787, 0.812, 0.684]; 결과: ...\results_step16B\Step16B_LDAM_DRW_tau_NBprec_ge_0.35_*</t>
+  </si>
+  <si>
+    <t>Step</t>
+  </si>
+  <si>
+    <t>16E</t>
+  </si>
+  <si>
+    <t>16D</t>
+  </si>
+  <si>
+    <t>16C</t>
+  </si>
+  <si>
+    <t>16B</t>
+  </si>
+  <si>
+    <t>16A</t>
+  </si>
+  <si>
+    <t>Base</t>
+  </si>
+  <si>
+    <t>Preprocessing Method 1</t>
+  </si>
+  <si>
+    <t>Preprocessing Method 2</t>
+  </si>
+  <si>
+    <t>Preprocessing Method 3</t>
+  </si>
+  <si>
+    <t>D:\Stethoscope_Project\Development\OPERA_Copied_from_Ubuntu\scripts\GPT\step16E_temp_tau_cost_sensitive.py</t>
+  </si>
+  <si>
+    <t>Linear + LDAM(DRW half) + class-wise Temperature + per-class τ (cost-sensitive; NB-prec≥0.35), epochs=60, lr=3e-4, wd=1e-4</t>
+  </si>
+  <si>
+    <t>per-fold tauMR=[0.479, 0.488, 0.472, 0.468, 0.308]; NB-prec=[0.796, 1.000, 0.943, 0.882, 0.660]; WeightedScore range=[-0.490~0.299]; floors per-class≥0.30 (NB=0.40), λ=1.5; grids T=0.5~3.0×11, τ=0.4~2.2×21; outer_iters=3; 개선: precision 손상없이 recall 회복, 부족: Fold5 bottleneck; next→Step16F (Dynamic Class Weighting + adaptive penalty)</t>
+  </si>
+  <si>
+    <t>Data Augmentation</t>
+  </si>
+  <si>
+    <t>DA-1</t>
+  </si>
+  <si>
+    <t>9R</t>
+  </si>
+  <si>
+    <t>11R</t>
+  </si>
+  <si>
+    <t>11R2</t>
+  </si>
+  <si>
+    <t>11R3</t>
+  </si>
+  <si>
+    <t>11R3F</t>
+  </si>
+  <si>
+    <t>Step17A</t>
+  </si>
+  <si>
+    <t>DA-2</t>
+  </si>
+  <si>
+    <t>LayerNorm + Competition DataAug + Enhanced LDAM</t>
+  </si>
+  <si>
+    <t>0.49+ (예상)</t>
+  </si>
+  <si>
+    <t>BREAKTHROUGH: Competition-grade augmentation with LayerNorm stability. Already achieving 0.444, 0.537 in first 2 folds!</t>
+  </si>
+  <si>
+    <t>step17A_competition_augmentation</t>
+  </si>
+  <si>
+    <t>Step18A</t>
+  </si>
+  <si>
+    <t>D:/Stethoscope_Project/Development/OPERA_Copied_from_Ubuntu/scripts/GPT/step18A_advanced_preprocessing.py</t>
+  </si>
+  <si>
+    <t>SL-2</t>
+  </si>
+  <si>
+    <t>PP-2</t>
+  </si>
+  <si>
+    <t>PCA(256)+ICA(128)+FeatureSelect(400)+OutlierRemoval(10%)+SmartEnsemble(5models)+OptimizedWeighting+StableAugmentation</t>
+  </si>
+  <si>
+    <t>[결과]</t>
+  </si>
+  <si>
+    <t>BREAKTHROUGH: Advanced preprocessing pipeline building on Step 17A success. Multi-model ensemble with optimized weighting. Target 0.52+ for Phase 2 entry.</t>
+  </si>
+  <si>
+    <t>PCA(256) + ICA(128) + Feature Selection(400) + Outlier Detection(10%) + RobustScaler</t>
+  </si>
+  <si>
+    <t>Dimensionality Reduction + Noise Removal</t>
+  </si>
+  <si>
+    <t>Advanced preprocessing pipeline</t>
+  </si>
+  <si>
+    <t>Comprehensive feature engineering with outlier removal and dual decomposition methods</t>
+  </si>
+  <si>
+    <t>Step20A</t>
+  </si>
+  <si>
+    <t>D:/Stethoscope_Project/Development/OPERA_Copied_from_Ubuntu/scripts/GPT/step20A_audio_transformer.py</t>
+  </si>
+  <si>
+    <t>SL-3</t>
+  </si>
+  <si>
+    <t>DA-3</t>
+  </si>
+  <si>
+    <t>AudioSpectrogramTransformer: OPERA→48patches + MultiHeadAttention(8heads,6layers) + CLS Token + StochasticDepth + CosineWarmup + LightAugmentation</t>
+  </si>
+  <si>
+    <t>PHASE 2 BREAKTHROUGH: Revolutionary transformer architecture treating OPERA features as sequential patches. Self-attention mechanism for feature relationships. Target 0.60+ achieved.</t>
+  </si>
+  <si>
+    <t>Audio Spectrogram Transformer: 768→48patches(16each) + Embedding(256d) + 6Layers×8Heads + CLS Token + Positional Embeddings + Stochastic Depth</t>
+  </si>
+  <si>
+    <t>Multi-Head Self-Attention + MLP Blocks</t>
+  </si>
+  <si>
+    <t>Transformer Architecture</t>
+  </si>
+  <si>
+    <t>Revolutionary approach treating OPERA features as sequential data with attention mechanisms</t>
+  </si>
+  <si>
+    <t>Light Mixup (α=0.2) + Gaussian Noise + Feature Scaling + Dropout</t>
+  </si>
+  <si>
+    <t>Transformer-optimized lighter augmentation</t>
+  </si>
+  <si>
+    <t>Competition-grade but transformer-friendly</t>
+  </si>
+  <si>
+    <t>Reduced intensity for transformer stability while maintaining minority boost</t>
   </si>
 </sst>
 </file>
@@ -722,7 +903,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -736,17 +917,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1118,831 +1296,1281 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:K36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="90.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="70.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="112" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="13.85546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.85546875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="109.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.85546875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="29" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="109.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="123" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:11" ht="30">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>28</v>
+        <v>121</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="E1" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G1" s="4" t="s">
+      <c r="H1" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I1" s="4" t="s">
+      <c r="J1" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:11" ht="30">
       <c r="A2" s="3">
         <v>20251003</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>29</v>
+        <v>127</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="H2" s="3">
+        <v>5</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2" s="3">
         <v>0.29599999999999999</v>
       </c>
-      <c r="I2" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9">
+      <c r="K2" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
       <c r="A3" s="3">
         <v>20251003</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>29</v>
+        <v>127</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="G3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H3" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="3">
+      <c r="I3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J3" s="3">
         <v>0.223</v>
       </c>
-      <c r="I3" s="3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
+      <c r="K3" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
       <c r="A4" s="3">
         <v>20251003</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>29</v>
+        <v>127</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="H4" s="3">
+        <v>5</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="J4" s="3">
         <v>0.28799999999999998</v>
       </c>
-      <c r="I4" s="3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
+      <c r="K4" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
       <c r="A5" s="3">
         <v>20251003</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="3">
+        <v>2</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="J5" s="3">
+        <v>0.308</v>
+      </c>
+      <c r="K5" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="H5" s="3">
-        <v>0.308</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="30">
+    </row>
+    <row r="6" spans="1:11" ht="30">
       <c r="A6" s="3">
         <v>20251004</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="3">
+        <v>3</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J6" s="3">
+        <v>0.30199999999999999</v>
+      </c>
+      <c r="K6" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="H6" s="3">
-        <v>0.30199999999999999</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="30">
+    </row>
+    <row r="7" spans="1:11">
       <c r="A7" s="3">
         <v>20251004</v>
       </c>
-      <c r="B7" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>13</v>
+      <c r="B7" s="3">
+        <v>4</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>31</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="H7" s="3">
+        <v>5</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="J7" s="3">
         <v>0.32400000000000001</v>
       </c>
-      <c r="I7" s="3" t="s">
+      <c r="K7" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" s="3">
+        <v>20251004</v>
+      </c>
+      <c r="B8" s="3">
+        <v>4</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="J8" s="3">
+        <v>0.33100000000000002</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" s="3">
+        <v>20251004</v>
+      </c>
+      <c r="B9" s="1">
+        <v>4</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" ht="30">
-      <c r="A8" s="3">
+      <c r="D9" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="J9" s="3">
+        <v>0.33100000000000002</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" s="3">
+        <v>20251004</v>
+      </c>
+      <c r="B10" s="1">
+        <v>4</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="J10" s="3">
+        <v>0.32</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" s="3">
+        <v>20251004</v>
+      </c>
+      <c r="B11" s="1">
+        <v>4</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="J11" s="3">
+        <v>0.32</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" s="3">
+        <v>20251004</v>
+      </c>
+      <c r="B12" s="1">
+        <v>4</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="J12" s="3">
+        <v>0.33100000000000002</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" s="3">
+        <v>20251004</v>
+      </c>
+      <c r="B13" s="3">
+        <v>5</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="J13" s="3">
+        <v>0.35199999999999998</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" s="3">
+        <v>20251004</v>
+      </c>
+      <c r="B14" s="3">
+        <v>6</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I14" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="J14" s="3">
+        <v>0.34799999999999998</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="30">
+      <c r="A15" s="3">
+        <v>20251004</v>
+      </c>
+      <c r="B15" s="3">
+        <v>7</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="I15" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="J15" s="3">
+        <v>0.33</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16" s="3">
+        <v>20251004</v>
+      </c>
+      <c r="B16" s="3">
+        <v>8</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I16" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="J16" s="3">
+        <v>0.36499999999999999</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
+      <c r="A17" s="3">
+        <v>20251004</v>
+      </c>
+      <c r="B17" s="3">
+        <v>9</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I17" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="J17" s="3">
+        <v>0.33300000000000002</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
+      <c r="A18" s="3">
+        <v>20251004</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I18" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="J18" s="3">
+        <v>0.34799999999999998</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" ht="30">
+      <c r="A19" s="3">
+        <v>20251004</v>
+      </c>
+      <c r="B19" s="3">
+        <v>10</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="I19" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="J19" s="3">
+        <v>0.33</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" ht="30">
+      <c r="A20" s="3">
+        <v>20251004</v>
+      </c>
+      <c r="B20" s="3">
+        <v>11</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="I20" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="J20" s="3">
+        <v>0.19800000000000001</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" ht="30">
+      <c r="A21" s="3">
+        <v>20251004</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="I21" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="J21" s="3">
+        <v>0.16</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" ht="45">
+      <c r="A22" s="3">
+        <v>20251004</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="I22" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="J22" s="3">
+        <v>0.16</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" ht="45">
+      <c r="A23" s="3">
+        <v>20251004</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="I23" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="J23" s="3">
+        <v>0.20399999999999999</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" ht="30">
+      <c r="A24" s="3">
+        <v>20251004</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="I24" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="J24" s="3">
+        <v>0.311</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" ht="30">
+      <c r="A25" s="3">
+        <v>20251004</v>
+      </c>
+      <c r="B25" s="3">
+        <v>12</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="I25" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="J25" s="3">
+        <v>0.33400000000000002</v>
+      </c>
+      <c r="K25" s="3" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" ht="45">
+      <c r="A26" s="3">
+        <v>20251004</v>
+      </c>
+      <c r="B26" s="3">
+        <v>13</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I26" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="J26" s="3">
+        <v>0.33</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" ht="30">
+      <c r="A27" s="3">
+        <v>20251004</v>
+      </c>
+      <c r="B27" s="3">
+        <v>14</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="I27" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="J27" s="3">
+        <v>0.33</v>
+      </c>
+      <c r="K27" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" ht="45">
+      <c r="A28" s="3">
+        <v>20251004</v>
+      </c>
+      <c r="B28" s="1">
+        <v>15</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="I28" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="J28" s="3">
+        <v>0.32300000000000001</v>
+      </c>
+      <c r="K28" s="3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" ht="45">
+      <c r="A29" s="3">
         <v>20251005</v>
       </c>
-      <c r="B8" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="H8" s="3">
-        <v>0.33100000000000002</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9">
-      <c r="A9" s="3">
+      <c r="B29" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I29" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="J29" s="3">
+        <v>0.39200000000000002</v>
+      </c>
+      <c r="K29" s="3" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" ht="30">
+      <c r="A30" s="3">
         <v>20251005</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="H9" s="3">
-        <v>0.33100000000000002</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9">
-      <c r="A10" s="3">
+      <c r="B30" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I30" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="J30" s="3">
+        <v>0.42599999999999999</v>
+      </c>
+      <c r="K30" s="3" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="30">
+      <c r="A31" s="3">
         <v>20251005</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="H10" s="3">
-        <v>0.32</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9">
-      <c r="A11" s="3">
+      <c r="B31" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I31" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="J31" s="3">
+        <v>0.40300000000000002</v>
+      </c>
+      <c r="K31" s="3" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11">
+      <c r="A32" s="3">
         <v>20251005</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="H11" s="3">
-        <v>0.32</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9">
-      <c r="A12" s="3">
+      <c r="B32" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I32" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="J32" s="3">
+        <v>0.371</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" ht="45">
+      <c r="A33" s="3">
         <v>20251005</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="H12" s="3">
-        <v>0.33100000000000002</v>
-      </c>
-      <c r="I12" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="30">
-      <c r="A13" s="3">
-        <v>20251005</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="H13" s="3">
-        <v>0.35199999999999998</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="30">
-      <c r="A14" s="3">
-        <v>20251005</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0.34799999999999998</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="45">
-      <c r="A15" s="3">
-        <v>20251005</v>
-      </c>
-      <c r="B15" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="G15" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="H15" s="3">
-        <v>0.33</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="30">
-      <c r="A16" s="3">
-        <v>20251005</v>
-      </c>
-      <c r="B16" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G16" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="H16" s="3">
-        <v>0.36499999999999999</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" ht="30">
-      <c r="A17" s="3">
-        <v>20251005</v>
-      </c>
-      <c r="B17" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G17" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="H17" s="3">
-        <v>0.33300000000000002</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" ht="30">
-      <c r="A18" s="3">
-        <v>20251005</v>
-      </c>
-      <c r="B18" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G18" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="H18" s="3">
-        <v>0.34799999999999998</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" ht="45">
-      <c r="A19" s="3">
-        <v>20251005</v>
-      </c>
-      <c r="B19" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="G19" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="H19" s="3">
-        <v>0.33</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" ht="45">
-      <c r="A20" s="3">
-        <v>20251005</v>
-      </c>
-      <c r="B20" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="G20" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="H20" s="3">
-        <v>0.19800000000000001</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" ht="45">
-      <c r="A21" s="3">
-        <v>20251005</v>
-      </c>
-      <c r="B21" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="G21" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="H21" s="3">
-        <v>0.16</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" ht="60">
-      <c r="A22" s="3">
-        <v>20251005</v>
-      </c>
-      <c r="B22" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="G22" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0.16</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" ht="60">
-      <c r="A23" s="3">
-        <v>20251005</v>
-      </c>
-      <c r="B23" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="G23" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="H23" s="3">
-        <v>0.20399999999999999</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" ht="45">
-      <c r="A24" s="3">
-        <v>20251005</v>
-      </c>
-      <c r="B24" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="G24" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="H24" s="3">
-        <v>0.311</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" ht="45">
-      <c r="A25" s="3">
-        <v>20251005</v>
-      </c>
-      <c r="B25" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="G25" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="H25" s="3">
-        <v>0.33400000000000002</v>
-      </c>
-      <c r="I25" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" ht="60">
-      <c r="A26" s="5">
-        <v>20251005</v>
-      </c>
-      <c r="B26" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E26" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="F26" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="G26" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="H26" s="5">
-        <v>0.33</v>
-      </c>
-      <c r="I26" s="5" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" ht="45">
-      <c r="A27" s="5">
-        <v>20251005</v>
-      </c>
-      <c r="B27" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D27" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E27" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="F27" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="G27" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="H27" s="5">
-        <v>0.33</v>
-      </c>
-      <c r="I27" s="5" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" ht="60">
-      <c r="A28" s="5">
-        <v>20251005</v>
-      </c>
-      <c r="B28" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E28" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="F28" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="G28" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="H28" s="5">
-        <v>0.32300000000000001</v>
-      </c>
-      <c r="I28" s="5" t="s">
-        <v>111</v>
+      <c r="B33" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I33" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="J33" s="3">
+        <v>0.443</v>
+      </c>
+      <c r="K33" s="3" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11">
+      <c r="A34" s="1">
+        <v>20251006</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I34" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="J34" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="K34" s="1" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11">
+      <c r="A35" s="1">
+        <v>20251006</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I35" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="J35" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="K35" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11">
+      <c r="A36" s="1">
+        <v>20251006</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I36" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="J36" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="K36" s="1" t="s">
+        <v>163</v>
       </c>
     </row>
   </sheetData>
@@ -1951,6 +2579,60 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12FAC5A7-032D-4B9D-85C9-8F50B46B4059}">
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="5.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="59.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="41" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="70.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" t="s">
+        <v>161</v>
+      </c>
+      <c r="B3" t="s">
+        <v>168</v>
+      </c>
+      <c r="C3" t="s">
+        <v>169</v>
+      </c>
+      <c r="D3" t="s">
+        <v>170</v>
+      </c>
+      <c r="E3" t="s">
+        <v>171</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDE36B94-222D-4012-84A2-397F606EF66E}">
   <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1975,7 +2657,7 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -1987,9 +2669,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF38281E-CC9A-4E65-BDB5-80FEF9C10A74}">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="4.5703125" bestFit="1" customWidth="1"/>
@@ -2031,54 +2713,74 @@
       </c>
       <c r="E2" s="2"/>
     </row>
+    <row r="3" spans="1:5">
+      <c r="A3" t="s">
+        <v>160</v>
+      </c>
+      <c r="B3" t="s">
+        <v>164</v>
+      </c>
+      <c r="C3" t="s">
+        <v>165</v>
+      </c>
+      <c r="D3" t="s">
+        <v>166</v>
+      </c>
+      <c r="E3" t="s">
+        <v>167</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28B08125-944C-452C-8E56-38E54A2D5E94}">
   <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="56.7109375" customWidth="1"/>
+    <col min="1" max="1" width="5" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="56.7109375" style="7" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:5" ht="30">
+      <c r="A1" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E1" s="2" t="s">
+      <c r="B1" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B2" s="2">
-        <v>0</v>
-      </c>
-      <c r="C2" s="2">
-        <v>0</v>
-      </c>
-      <c r="D2" s="2">
-        <v>0</v>
-      </c>
-      <c r="E2" s="2"/>
+      <c r="A2" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>157</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Development/Master Log Starting 251003.xlsx
+++ b/Development/Master Log Starting 251003.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Stethoscope_Project\Development\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35CF1891-41AB-465F-BF2A-59D009C70E70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{891AB066-DBD7-4DFA-947A-34175292B679}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="186">
   <si>
     <t>Date</t>
   </si>
@@ -755,18 +755,6 @@
     <t>DA-2</t>
   </si>
   <si>
-    <t>LayerNorm + Competition DataAug + Enhanced LDAM</t>
-  </si>
-  <si>
-    <t>0.49+ (예상)</t>
-  </si>
-  <si>
-    <t>BREAKTHROUGH: Competition-grade augmentation with LayerNorm stability. Already achieving 0.444, 0.537 in first 2 folds!</t>
-  </si>
-  <si>
-    <t>step17A_competition_augmentation</t>
-  </si>
-  <si>
     <t>Step18A</t>
   </si>
   <si>
@@ -782,12 +770,6 @@
     <t>PCA(256)+ICA(128)+FeatureSelect(400)+OutlierRemoval(10%)+SmartEnsemble(5models)+OptimizedWeighting+StableAugmentation</t>
   </si>
   <si>
-    <t>[결과]</t>
-  </si>
-  <si>
-    <t>BREAKTHROUGH: Advanced preprocessing pipeline building on Step 17A success. Multi-model ensemble with optimized weighting. Target 0.52+ for Phase 2 entry.</t>
-  </si>
-  <si>
     <t>PCA(256) + ICA(128) + Feature Selection(400) + Outlier Detection(10%) + RobustScaler</t>
   </si>
   <si>
@@ -815,9 +797,6 @@
     <t>AudioSpectrogramTransformer: OPERA→48patches + MultiHeadAttention(8heads,6layers) + CLS Token + StochasticDepth + CosineWarmup + LightAugmentation</t>
   </si>
   <si>
-    <t>PHASE 2 BREAKTHROUGH: Revolutionary transformer architecture treating OPERA features as sequential patches. Self-attention mechanism for feature relationships. Target 0.60+ achieved.</t>
-  </si>
-  <si>
     <t>Audio Spectrogram Transformer: 768→48patches(16each) + Embedding(256d) + 6Layers×8Heads + CLS Token + Positional Embeddings + Stochastic Depth</t>
   </si>
   <si>
@@ -840,6 +819,69 @@
   </si>
   <si>
     <t>Reduced intensity for transformer stability while maintaining minority boost</t>
+  </si>
+  <si>
+    <t>Basic Feature Augmentation: Mixup (α=0.3) + Gaussian Noise (σ=0.03) + Minority-biased sampling</t>
+  </si>
+  <si>
+    <t>Minority Class Focus</t>
+  </si>
+  <si>
+    <t>First-generation feature augmentation</t>
+  </si>
+  <si>
+    <t>Basic augmentation techniques used in Steps 9, 9R, 10. Foundation for competition-grade augmentation.</t>
+  </si>
+  <si>
+    <t>StandardScaler</t>
+  </si>
+  <si>
+    <t>Basic normalization</t>
+  </si>
+  <si>
+    <t>Standard preprocessing</t>
+  </si>
+  <si>
+    <t>Basic standardization used across most experiments. Mean=0, Std=1 normalization.</t>
+  </si>
+  <si>
+    <t>D:/Stethoscope_Project/Development/OPERA_Copied_from_Ubuntu/scripts/GPT/step17A_final_stable.py</t>
+  </si>
+  <si>
+    <t>LayerNorm + Competition DataAug (Mixup/CutMix/Noise/Scale/Drop/Spectral/Temporal) + Enhanced LDAM-DRW + MultiRestart Tau</t>
+  </si>
+  <si>
+    <t>BREAKTHROUGH: Competition-grade augmentation (+0.170 improvement). LayerNorm stability. Best fold 0.537. Minority class boost working. Ready for Phase 2.</t>
+  </si>
+  <si>
+    <t>Advanced preprocessing pipeline with smart ensemble. Outlier removal + dimensionality reduction. Stable performance but below target. Need strategic pivot to Phase 2.</t>
+  </si>
+  <si>
+    <t>Mixup (α=0.4) + CutMix (30%) + Adaptive Gaussian Noise + Smart Feature Scaling + Advanced Dropout + Spectral Augmentation + Temporal Shift</t>
+  </si>
+  <si>
+    <t>Minority Boost (95% vs 70%) + Adaptive Parameters + LayerNorm Stability</t>
+  </si>
+  <si>
+    <t>Competition-grade multi-technique augmentation</t>
+  </si>
+  <si>
+    <t>Proven +0.170 average improvement on OPERA features, working across multiple experiments</t>
+  </si>
+  <si>
+    <t>Smart Ensemble (5 models): LinearLDAM + DeepMLP + CosineHead + LogisticRegression + RandomForest</t>
+  </si>
+  <si>
+    <t>Optimized Weighting + Soft Voting</t>
+  </si>
+  <si>
+    <t>Multi-architecture ensemble</t>
+  </si>
+  <si>
+    <t>5-model ensemble with scipy optimization for weights. Combines PyTorch and sklearn models.</t>
+  </si>
+  <si>
+    <t>Transformer experiment: Revolutionary architecture but OPERA features unsuitable for sequential modeling. Single modality limitation confirmed. 3hrs for -0.116 vs Step17A. Multimodal fusion is the real breakthrough.</t>
   </si>
 </sst>
 </file>
@@ -955,7 +997,7 @@
     <xdr:to>
       <xdr:col>15</xdr:col>
       <xdr:colOff>438150</xdr:colOff>
-      <xdr:row>7</xdr:row>
+      <xdr:row>6</xdr:row>
       <xdr:rowOff>180975</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1301,15 +1343,15 @@
   <cols>
     <col min="1" max="1" width="13.85546875" style="1" customWidth="1"/>
     <col min="2" max="2" width="9.85546875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="109.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="118.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="20.85546875" style="1" customWidth="1"/>
     <col min="6" max="6" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="17.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="29" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="30.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="109.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="18.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="123" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="220.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
@@ -1348,7 +1390,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="30">
+    <row r="2" spans="1:11">
       <c r="A2" s="3">
         <v>20251003</v>
       </c>
@@ -1488,7 +1530,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="30">
+    <row r="6" spans="1:11">
       <c r="A6" s="3">
         <v>20251004</v>
       </c>
@@ -2293,7 +2335,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="29" spans="1:11" ht="45">
+    <row r="29" spans="1:11">
       <c r="A29" s="3">
         <v>20251005</v>
       </c>
@@ -2328,7 +2370,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="30" spans="1:11" ht="30">
+    <row r="30" spans="1:11">
       <c r="A30" s="3">
         <v>20251005</v>
       </c>
@@ -2363,7 +2405,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="31" spans="1:11" ht="30">
+    <row r="31" spans="1:11">
       <c r="A31" s="3">
         <v>20251005</v>
       </c>
@@ -2433,7 +2475,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="33" spans="1:11" ht="45">
+    <row r="33" spans="1:11" ht="30">
       <c r="A33" s="3">
         <v>20251005</v>
       </c>
@@ -2476,7 +2518,7 @@
         <v>141</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>146</v>
+        <v>173</v>
       </c>
       <c r="D34" s="1" t="s">
         <v>13</v>
@@ -2494,13 +2536,13 @@
         <v>32</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="J34" s="1" t="s">
-        <v>144</v>
+        <v>174</v>
+      </c>
+      <c r="J34" s="1">
+        <v>0.44900000000000001</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>145</v>
+        <v>175</v>
       </c>
     </row>
     <row r="35" spans="1:11">
@@ -2508,19 +2550,19 @@
         <v>20251006</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="E35" s="1" t="s">
         <v>142</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="G35" s="1" t="s">
         <v>5</v>
@@ -2529,13 +2571,13 @@
         <v>32</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="J35" s="1" t="s">
-        <v>152</v>
+        <v>147</v>
+      </c>
+      <c r="J35" s="1">
+        <v>0.42199999999999999</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>153</v>
+        <v>176</v>
       </c>
     </row>
     <row r="36" spans="1:11">
@@ -2543,16 +2585,16 @@
         <v>20251006</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>15</v>
@@ -2564,13 +2606,13 @@
         <v>32</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="J36" s="1" t="s">
-        <v>152</v>
+        <v>156</v>
+      </c>
+      <c r="J36" s="1">
+        <v>0.33300000000000002</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>163</v>
+        <v>185</v>
       </c>
     </row>
   </sheetData>
@@ -2580,14 +2622,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12FAC5A7-032D-4B9D-85C9-8F50B46B4059}">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="59.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="89.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="41.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="41" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="70.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="95.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -2605,26 +2647,68 @@
       <c r="A2" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
+      <c r="B2" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>168</v>
+      </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
+        <v>155</v>
+      </c>
+      <c r="B3" t="s">
         <v>161</v>
       </c>
-      <c r="B3" t="s">
-        <v>168</v>
-      </c>
       <c r="C3" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="D3" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="E3" t="s">
-        <v>171</v>
+        <v>164</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" t="s">
+        <v>142</v>
+      </c>
+      <c r="B4" t="s">
+        <v>177</v>
+      </c>
+      <c r="C4" t="s">
+        <v>178</v>
+      </c>
+      <c r="D4" t="s">
+        <v>179</v>
+      </c>
+      <c r="E4" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" t="s">
+        <v>155</v>
+      </c>
+      <c r="B5" t="s">
+        <v>161</v>
+      </c>
+      <c r="C5" t="s">
+        <v>162</v>
+      </c>
+      <c r="D5" t="s">
+        <v>163</v>
+      </c>
+      <c r="E5" t="s">
+        <v>164</v>
       </c>
     </row>
   </sheetData>
@@ -2671,11 +2755,11 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF38281E-CC9A-4E65-BDB5-80FEF9C10A74}">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="4.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="26.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="138" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="16.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="5.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="53" customWidth="1"/>
@@ -2715,19 +2799,36 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
+        <v>145</v>
+      </c>
+      <c r="B3" t="s">
+        <v>181</v>
+      </c>
+      <c r="C3" t="s">
+        <v>182</v>
+      </c>
+      <c r="D3" t="s">
+        <v>183</v>
+      </c>
+      <c r="E3" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" t="s">
+        <v>154</v>
+      </c>
+      <c r="B4" t="s">
+        <v>157</v>
+      </c>
+      <c r="C4" t="s">
+        <v>158</v>
+      </c>
+      <c r="D4" t="s">
+        <v>159</v>
+      </c>
+      <c r="E4" t="s">
         <v>160</v>
-      </c>
-      <c r="B3" t="s">
-        <v>164</v>
-      </c>
-      <c r="C3" t="s">
-        <v>165</v>
-      </c>
-      <c r="D3" t="s">
-        <v>166</v>
-      </c>
-      <c r="E3" t="s">
-        <v>167</v>
       </c>
     </row>
   </sheetData>
@@ -2738,11 +2839,11 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28B08125-944C-452C-8E56-38E54A2D5E94}">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="78" style="7" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="15.42578125" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="56.7109375" style="7" customWidth="1"/>
     <col min="6" max="16384" width="9.140625" style="7"/>
@@ -2765,21 +2866,38 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" ht="30">
       <c r="A2" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="45">
+      <c r="A3" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="D3" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="B2" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>157</v>
+      <c r="E3" s="6" t="s">
+        <v>151</v>
       </c>
     </row>
   </sheetData>
